--- a/sheets/민요/검수/창부 타령 (1절 굿거리).xlsx
+++ b/sheets/민요/검수/창부 타령 (1절 굿거리).xlsx
@@ -4,17 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
-    <sheet name="악보 3" sheetId="5" r:id="rId5"/>
-    <sheet name="악보 4" sheetId="6" r:id="rId6"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -23,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -53,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -76,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +176,66 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13410,8 +13547,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U56"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -13434,3236 +13575,3047 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">창부 타령 — 민요채보-1/창부 타령.jpg (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">창부 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E3" s="20"/>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G3" s="20"/>
+      <c r="H3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="K3" s="20"/>
+      <c r="L3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="M3" s="20"/>
+      <c r="N3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="P3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="R3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="T3" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E4" s="21"/>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G4" s="21"/>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I4" s="21"/>
+      <c r="J4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K4" s="21"/>
+      <c r="L4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M4" s="21"/>
+      <c r="N4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O4" s="21"/>
+      <c r="P4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q4" s="21"/>
+      <c r="R4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S4" s="21"/>
+      <c r="T4" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="U4" s="21"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E5" s="22"/>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G5" s="22"/>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I5" s="22"/>
+      <c r="J5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K5" s="22"/>
+      <c r="L5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M5" s="22"/>
+      <c r="N5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O5" s="22"/>
+      <c r="P5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S5" s="22"/>
+      <c r="T5" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U5" s="22"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">강</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="20"/>
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">놀</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="P6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="R6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="T6" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U6" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="C7" s="21"/>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E7" s="21"/>
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G7" s="21"/>
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="21"/>
+      <c r="J7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K7" s="21"/>
+      <c r="L7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M7" s="21"/>
+      <c r="N7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O7" s="21"/>
+      <c r="P7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="Q7" s="21"/>
+      <c r="R7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="S7" s="21"/>
+      <c r="T7" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U7" s="21"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="C8" s="22"/>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E8" s="22"/>
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="22"/>
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="22"/>
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K8" s="22"/>
+      <c r="L8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="22"/>
+      <c r="N8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="O8" s="22"/>
+      <c r="P8" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S8" s="22"/>
+      <c r="T8" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U8" s="22"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="E9" s="20"/>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">못</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="P9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="R9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="T9" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E10" s="21"/>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G10" s="21"/>
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="21"/>
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="21"/>
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="M10" s="21"/>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O10" s="21"/>
+      <c r="P10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="Q10" s="21"/>
+      <c r="R10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="S10" s="21"/>
+      <c r="T10" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="U10" s="21"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E11" s="22"/>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G11" s="22"/>
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="22"/>
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="22"/>
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="22"/>
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="O11" s="22"/>
+      <c r="P11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="S11" s="22"/>
+      <c r="T11" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U11" s="22"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="C12" s="20"/>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E12" s="20"/>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G12" s="20"/>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I12" s="20"/>
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K12" s="20"/>
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="U14" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">창부 타령 — 민요채보-1/창부 타령.jpg (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="M12" s="20"/>
+      <c r="N12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O12" s="20"/>
+      <c r="P12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S12" s="20"/>
+      <c r="T12" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U12" s="20"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C13" s="21"/>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E13" s="21"/>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G13" s="21"/>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I13" s="21"/>
+      <c r="J13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K13" s="21"/>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M13" s="21"/>
+      <c r="N13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O13" s="21"/>
+      <c r="P13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S13" s="21"/>
+      <c r="T13" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U13" s="21"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E14" s="22"/>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G14" s="22"/>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I14" s="22"/>
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K14" s="22"/>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M14" s="22"/>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O14" s="22"/>
+      <c r="P14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S14" s="22"/>
+      <c r="T14" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="U14" s="22"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">창부 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C16"/>
+      <c s="8" r="D16"/>
+      <c s="8" r="E16"/>
+      <c s="8" r="F16"/>
+      <c s="8" r="G16"/>
+      <c s="8" r="H16"/>
+      <c s="8" r="I16"/>
+      <c s="8" r="J16"/>
+      <c s="8" r="K16"/>
+      <c s="8" r="L16"/>
+      <c s="8" r="M16"/>
+      <c s="8" r="N16"/>
+      <c s="8" r="O16"/>
+      <c s="8" r="P16"/>
+      <c s="8" r="Q16"/>
+      <c s="8" r="R16"/>
+      <c s="8" r="S16"/>
+      <c s="8" r="T16"/>
+      <c s="8" r="U16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="18"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="N17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="O17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="P17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q17" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">밤</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="R17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="S17" s="20"/>
+      <c r="T17" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U17" s="20"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="18"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M18" s="21"/>
+      <c r="N18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O18" s="21"/>
+      <c r="P18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S18" s="21"/>
+      <c r="T18" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U18" s="21"/>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="18"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M19" s="22"/>
+      <c r="N19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O19" s="22"/>
+      <c r="P19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S19" s="22"/>
+      <c r="T19" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U19" s="22"/>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="B20" s="18"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="N20" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O20" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="P20" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="Q20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="R20" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="S20" s="20"/>
+      <c r="T20" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K6" s="2"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="U20" s="20"/>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="18"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M21" s="21"/>
+      <c r="N21" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O21" s="21"/>
+      <c r="P21" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="Q21" s="21"/>
+      <c r="R21" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="S21" s="21"/>
+      <c r="T21" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="U21" s="21"/>
+    </row>
+    <row r="22" ht="56" customHeight="1">
+      <c r="B22" s="18"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M22" s="22"/>
+      <c r="N22" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O22" s="22"/>
+      <c r="P22" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="S22" s="22"/>
+      <c r="T22" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="U22" s="22"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="B23" s="18"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M23" s="20"/>
+      <c r="N23" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O23" s="20"/>
+      <c r="P23" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q23" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="R23" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="S23" s="20"/>
+      <c r="T23" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="U23" s="20"/>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="B24" s="18"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M24" s="21"/>
+      <c r="N24" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O24" s="21"/>
+      <c r="P24" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q24" s="21"/>
+      <c r="R24" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S24" s="21"/>
+      <c r="T24" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U24" s="21"/>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="B25" s="18"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M25" s="22"/>
+      <c r="N25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O25" s="22"/>
+      <c r="P25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q25" s="22"/>
+      <c r="R25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S25" s="22"/>
+      <c r="T25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U25" s="22"/>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="B26" s="18"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M26" s="20"/>
+      <c r="N26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O26" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="P26" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="Q26" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="R26" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S26" s="20"/>
+      <c r="T26" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U26" s="20"/>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="B27" s="18"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M27" s="21"/>
+      <c r="N27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O27" s="21"/>
+      <c r="P27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q27" s="21"/>
+      <c r="R27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S27" s="21"/>
+      <c r="T27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U27" s="21"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="B28" s="18"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
-    <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
-    <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
-    <col min="21" max="21" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">창부 타령 — 민요채보-1/창부 타령-2.jpg (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="M28" s="22"/>
+      <c r="N28" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O28" s="22"/>
+      <c r="P28" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S28" s="22"/>
+      <c r="T28" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U28" s="22"/>
+    </row>
+    <row r="29"/>
+    <row r="30" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B30">
+        <is>
+          <t xml:space="preserve">창부 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C30"/>
+      <c s="8" r="D30"/>
+      <c s="8" r="E30"/>
+      <c s="8" r="F30"/>
+      <c s="8" r="G30"/>
+      <c s="8" r="H30"/>
+      <c s="8" r="I30"/>
+      <c s="8" r="J30"/>
+      <c s="8" r="K30"/>
+      <c s="8" r="L30"/>
+      <c s="8" r="M30"/>
+      <c s="8" r="N30"/>
+      <c s="8" r="O30"/>
+      <c s="8" r="P30"/>
+      <c s="8" r="Q30"/>
+      <c s="8" r="R30"/>
+      <c s="8" r="S30"/>
+      <c s="8" r="T30"/>
+      <c s="8" r="U30"/>
+    </row>
+    <row r="31" ht="56" customHeight="1">
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E31" s="20"/>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G31" s="20"/>
+      <c r="H31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J31" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K31" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">소</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L31" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="M31" s="20"/>
+      <c r="N31" s="19" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 沖</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="O31" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P31" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q31" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="R31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S31" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">줄</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="T31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U31" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">남</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
+    <row r="32" ht="56" customHeight="1">
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C32" s="21"/>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E32" s="21"/>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G32" s="21"/>
+      <c r="H32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I32" s="21"/>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K32" s="21"/>
+      <c r="L32" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M32" s="21"/>
+      <c r="N32" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="O32" s="21"/>
+      <c r="P32" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="Q32" s="21"/>
+      <c r="R32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S32" s="21"/>
+      <c r="T32" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U32" s="21"/>
+    </row>
+    <row r="33" ht="56" customHeight="1">
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C33" s="22"/>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E33" s="22"/>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G33" s="22"/>
+      <c r="H33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I33" s="22"/>
+      <c r="J33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K33" s="22"/>
+      <c r="L33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M33" s="22"/>
+      <c r="N33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O33" s="22"/>
+      <c r="P33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q33" s="22"/>
+      <c r="R33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S33" s="22"/>
+      <c r="T33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U33" s="22"/>
+    </row>
+    <row r="34" ht="56" customHeight="1">
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C34" s="20"/>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E34" s="20"/>
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G34" s="20"/>
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J34" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K34" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">근</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L34" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M34" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">래</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N34" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O34" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="P34" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S34" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">주</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="T34" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U34" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
+    <row r="35" ht="56" customHeight="1">
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C35" s="21"/>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E35" s="21"/>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G35" s="21"/>
+      <c r="H35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I35" s="21"/>
+      <c r="J35" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="K35" s="21"/>
+      <c r="L35" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M35" s="21"/>
+      <c r="N35" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O35" s="21"/>
+      <c r="P35" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="Q35" s="21"/>
+      <c r="R35" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S35" s="21"/>
+      <c r="T35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U35" s="21"/>
+    </row>
+    <row r="36" ht="56" customHeight="1">
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C36" s="22"/>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E36" s="22"/>
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G36" s="22"/>
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I36" s="22"/>
+      <c r="J36" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="K36" s="22"/>
+      <c r="L36" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M36" s="22"/>
+      <c r="N36" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="O36" s="22"/>
+      <c r="P36" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="Q36" s="22"/>
+      <c r="R36" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S36" s="22"/>
+      <c r="T36" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U36" s="22"/>
+    </row>
+    <row r="37" ht="56" customHeight="1">
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C37" s="20"/>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E37" s="20"/>
+      <c r="F37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="J37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K37" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M37" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="N37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O37" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="P37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q37" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="R37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S37" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="T37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U37" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+    <row r="38" ht="56" customHeight="1">
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C38" s="21"/>
+      <c r="D38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E38" s="21"/>
+      <c r="F38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G38" s="21"/>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I38" s="21"/>
+      <c r="J38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K38" s="21"/>
+      <c r="L38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M38" s="21"/>
+      <c r="N38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O38" s="21"/>
+      <c r="P38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q38" s="21"/>
+      <c r="R38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S38" s="21"/>
+      <c r="T38" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="U38" s="21"/>
+    </row>
+    <row r="39" ht="56" customHeight="1">
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C39" s="22"/>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E39" s="22"/>
+      <c r="F39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G39" s="22"/>
+      <c r="H39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I39" s="22"/>
+      <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K39" s="22"/>
+      <c r="L39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M39" s="22"/>
+      <c r="N39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O39" s="22"/>
+      <c r="P39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q39" s="22"/>
+      <c r="R39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S39" s="22"/>
+      <c r="T39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U39" s="22"/>
+    </row>
+    <row r="40" ht="56" customHeight="1">
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C40" s="20"/>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E40" s="20"/>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G40" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I40" s="20"/>
+      <c r="J40" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K40" s="20"/>
+      <c r="L40" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="M40" s="20"/>
+      <c r="N40" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="O40" s="20"/>
+      <c r="P40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q40" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="R40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S40" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">모</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="T40" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U40" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+    <row r="41" ht="56" customHeight="1">
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C41" s="21"/>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E41" s="21"/>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G41" s="21"/>
+      <c r="H41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I41" s="21"/>
+      <c r="J41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K41" s="21"/>
+      <c r="L41" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M41" s="21"/>
+      <c r="N41" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O41" s="21"/>
+      <c r="P41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q41" s="21"/>
+      <c r="R41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S41" s="21"/>
+      <c r="T41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U41" s="21"/>
+    </row>
+    <row r="42" ht="56" customHeight="1">
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C42" s="22"/>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E42" s="22"/>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G42" s="22"/>
+      <c r="H42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I42" s="22"/>
+      <c r="J42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="K42" s="22"/>
+      <c r="L42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M42" s="22"/>
+      <c r="N42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O42" s="22"/>
+      <c r="P42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q42" s="22"/>
+      <c r="R42" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S42" s="22"/>
+      <c r="T42" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="U14" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
-    <col min="11" max="11" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">창부 타령 — 민요채보-1/창부 타령-2.jpg (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="U42" s="22"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B44">
+        <is>
+          <t xml:space="preserve">창부 타령</t>
+        </is>
+      </c>
+      <c s="8" r="C44"/>
+      <c s="8" r="D44"/>
+      <c s="8" r="E44"/>
+      <c s="8" r="F44"/>
+      <c s="8" r="G44"/>
+      <c s="8" r="H44"/>
+      <c s="8" r="I44"/>
+      <c s="8" r="J44"/>
+      <c s="8" r="K44"/>
+      <c s="8" r="L44"/>
+      <c s="8" r="M44"/>
+      <c s="8" r="N44"/>
+      <c s="8" r="O44"/>
+      <c s="8" r="P44"/>
+      <c s="8" r="Q44"/>
+      <c s="8" r="R44"/>
+      <c s="8" r="S44"/>
+      <c s="8" r="T44"/>
+      <c s="8" r="U44"/>
+    </row>
+    <row r="45" ht="56" customHeight="1">
+      <c r="B45" s="18"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="23"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="23"/>
+      <c r="L45" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="M45" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">광</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="N45" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="O45" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="P45" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q45" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="R45" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="S45" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="T45" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U45" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
+    <row r="46" ht="56" customHeight="1">
+      <c r="B46" s="18"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="18"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="24"/>
+      <c r="L46" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M46" s="21"/>
+      <c r="N46" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="O46" s="21"/>
+      <c r="P46" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q46" s="21"/>
+      <c r="R46" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S46" s="21"/>
+      <c r="T46" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U46" s="21"/>
+    </row>
+    <row r="47" ht="56" customHeight="1">
+      <c r="B47" s="18"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="25"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="25"/>
+      <c r="L47" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M47" s="22"/>
+      <c r="N47" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O47" s="22"/>
+      <c r="P47" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q47" s="22"/>
+      <c r="R47" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S47" s="22"/>
+      <c r="T47" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U47" s="22"/>
+    </row>
+    <row r="48" ht="56" customHeight="1">
+      <c r="B48" s="18"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="18"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="18"/>
+      <c r="I48" s="23"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="23"/>
+      <c r="L48" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="M48" s="20"/>
+      <c r="N48" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="O48" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="P48" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="Q48" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="R48" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="S48" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="T48" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="U48" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="49" ht="56" customHeight="1">
+      <c r="B49" s="18"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="24"/>
+      <c r="L49" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="M49" s="21"/>
+      <c r="N49" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O49" s="21"/>
+      <c r="P49" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q49" s="21"/>
+      <c r="R49" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="S49" s="21"/>
+      <c r="T49" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U49" s="21"/>
+    </row>
+    <row r="50" ht="56" customHeight="1">
+      <c r="B50" s="18"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="25"/>
+      <c r="L50" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="M50" s="22"/>
+      <c r="N50" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="O50" s="22"/>
+      <c r="P50" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="Q50" s="22"/>
+      <c r="R50" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="S50" s="22"/>
+      <c r="T50" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U50" s="22"/>
+    </row>
+    <row r="51" ht="56" customHeight="1">
+      <c r="B51" s="18"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="18"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="18"/>
+      <c r="I51" s="23"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="23"/>
+      <c r="L51" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M51" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">것</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="N51" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O51" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="P51" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q51" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="R51" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S51" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="T51" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U51" s="20"/>
+    </row>
+    <row r="52" ht="56" customHeight="1">
+      <c r="B52" s="18"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="18"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="24"/>
+      <c r="L52" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="M52" s="21"/>
+      <c r="N52" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O52" s="21"/>
+      <c r="P52" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q52" s="21"/>
+      <c r="R52" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="S52" s="21"/>
+      <c r="T52" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U52" s="21"/>
+    </row>
+    <row r="53" ht="56" customHeight="1">
+      <c r="B53" s="18"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="18"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="25"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="25"/>
+      <c r="L53" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="M53" s="22"/>
+      <c r="N53" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="O53" s="22"/>
+      <c r="P53" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q53" s="22"/>
+      <c r="R53" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S53" s="22"/>
+      <c r="T53" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U53" s="22"/>
+    </row>
+    <row r="54" ht="56" customHeight="1">
+      <c r="B54" s="18"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="23"/>
+      <c r="L54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M54" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="N54" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="O54" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="P54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="Q54" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="R54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="S54" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="T54" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="U54" s="20"/>
+    </row>
+    <row r="55" ht="56" customHeight="1">
+      <c r="B55" s="18"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="24"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="24"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="24"/>
+      <c r="L55" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M55" s="21"/>
+      <c r="N55" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O55" s="21"/>
+      <c r="P55" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q55" s="21"/>
+      <c r="R55" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S55" s="21"/>
+      <c r="T55" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U55" s="21"/>
+    </row>
+    <row r="56" ht="56" customHeight="1">
+      <c r="B56" s="18"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="25"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="25"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="25"/>
+      <c r="L56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M56" s="22"/>
+      <c r="N56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O56" s="22"/>
+      <c r="P56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q56" s="22"/>
+      <c r="R56" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
+      <c r="S56" s="22"/>
+      <c r="T56" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="U56" s="22"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B16:U16"/>
+    <mergeCell ref="B30:U30"/>
+    <mergeCell ref="B44:U44"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="14" max="16383" man="1"/>
+    <brk id="28" max="16383" man="1"/>
+    <brk id="42" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>